--- a/output/graficos_regionales/plot_regional_serie_i_ingr_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_a_2024_antofagasta.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:35</t>
+    <t xml:space="preserve">2026-10-05 01:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -470,7 +470,7 @@
         <v>1022175.75</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>812081.12</v>
+        <v>812081.13</v>
       </c>
     </row>
     <row r="3">
@@ -489,7 +489,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1108679.12</v>
+        <v>1108679.13</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>898522.25</v>
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1271792.12</v>
+        <v>1271792.13</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>1060428.38</v>
@@ -522,10 +522,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1419730.62</v>
+        <v>1419730.63</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1190492.62</v>
+        <v>1190492.63</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1503485.12</v>
+        <v>1503485.13</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>1268050.25</v>
